--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/47.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/47.xlsx
@@ -426,13 +426,13 @@
         <v>-14.0402525514349</v>
       </c>
       <c r="E2">
-        <v>-18.42562089385893</v>
+        <v>-14.82963347284866</v>
       </c>
       <c r="F2">
-        <v>0.9871992497321779</v>
+        <v>1.688408942732348</v>
       </c>
       <c r="G2">
-        <v>-15.45117308553356</v>
+        <v>-14.75318138149336</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.73236069670738</v>
       </c>
       <c r="E3">
-        <v>-18.11852829528978</v>
+        <v>-16.07825907875643</v>
       </c>
       <c r="F3">
-        <v>1.142082416503213</v>
+        <v>1.87923994131527</v>
       </c>
       <c r="G3">
-        <v>-15.22187922032986</v>
+        <v>-14.66698634344546</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.31706681718402</v>
       </c>
       <c r="E4">
-        <v>-18.62512870626971</v>
+        <v>-16.13454755184183</v>
       </c>
       <c r="F4">
-        <v>1.902477303698602</v>
+        <v>1.897570055204418</v>
       </c>
       <c r="G4">
-        <v>-14.69206776673228</v>
+        <v>-13.79516734841204</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.81175338697273</v>
       </c>
       <c r="E5">
-        <v>-18.40590559969996</v>
+        <v>-16.79809366557572</v>
       </c>
       <c r="F5">
-        <v>1.950612076740476</v>
+        <v>1.844718558171004</v>
       </c>
       <c r="G5">
-        <v>-15.1589681079178</v>
+        <v>-13.70196115576471</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.2224734197335</v>
       </c>
       <c r="E6">
-        <v>-19.31091526664805</v>
+        <v>-17.55042297780046</v>
       </c>
       <c r="F6">
-        <v>2.110904482651791</v>
+        <v>2.01019820075865</v>
       </c>
       <c r="G6">
-        <v>-14.59812795485484</v>
+        <v>-13.3686395615835</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.57199467207656</v>
       </c>
       <c r="E7">
-        <v>-21.84682041626379</v>
+        <v>-18.20246884937589</v>
       </c>
       <c r="F7">
-        <v>1.243159806992808</v>
+        <v>2.05463017151001</v>
       </c>
       <c r="G7">
-        <v>-14.25941647846528</v>
+        <v>-13.16431224690461</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.85660708534011</v>
       </c>
       <c r="E8">
-        <v>-20.46581950579975</v>
+        <v>-18.48706350219844</v>
       </c>
       <c r="F8">
-        <v>2.074332061818193</v>
+        <v>2.140195554014782</v>
       </c>
       <c r="G8">
-        <v>-13.60987236180237</v>
+        <v>-12.87215426269149</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.10524535380954</v>
       </c>
       <c r="E9">
-        <v>-21.22638878929295</v>
+        <v>-18.79367848146523</v>
       </c>
       <c r="F9">
-        <v>1.632722772446554</v>
+        <v>2.080241634869765</v>
       </c>
       <c r="G9">
-        <v>-12.65296920054457</v>
+        <v>-12.1658421156394</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.320626113279646</v>
       </c>
       <c r="E10">
-        <v>-20.95456941450557</v>
+        <v>-20.38920521649064</v>
       </c>
       <c r="F10">
-        <v>1.462501554845284</v>
+        <v>2.192483761214292</v>
       </c>
       <c r="G10">
-        <v>-12.07472190792037</v>
+        <v>-12.22857047593008</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.520841840448515</v>
       </c>
       <c r="E11">
-        <v>-20.40978437860516</v>
+        <v>-20.64028345392182</v>
       </c>
       <c r="F11">
-        <v>2.822188780004809</v>
+        <v>2.468237329197414</v>
       </c>
       <c r="G11">
-        <v>-11.84002380141306</v>
+        <v>-11.32198027905992</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.724170609990569</v>
       </c>
       <c r="E12">
-        <v>-22.95442373163701</v>
+        <v>-20.52934702622433</v>
       </c>
       <c r="F12">
-        <v>2.468081596125688</v>
+        <v>2.521300888285945</v>
       </c>
       <c r="G12">
-        <v>-11.98069333072683</v>
+        <v>-10.91917371758624</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.934107769667312</v>
       </c>
       <c r="E13">
-        <v>-24.14054766031744</v>
+        <v>-21.76700815423456</v>
       </c>
       <c r="F13">
-        <v>2.585610363234882</v>
+        <v>2.854059387460117</v>
       </c>
       <c r="G13">
-        <v>-11.84069345740068</v>
+        <v>-10.28803535029067</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.177772644450253</v>
       </c>
       <c r="E14">
-        <v>-23.72142218626105</v>
+        <v>-23.46641501091657</v>
       </c>
       <c r="F14">
-        <v>3.097191847120995</v>
+        <v>2.837573219409601</v>
       </c>
       <c r="G14">
-        <v>-9.398699564423179</v>
+        <v>-9.897555419403924</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.456696362872006</v>
       </c>
       <c r="E15">
-        <v>-26.03922144315341</v>
+        <v>-23.67375162667467</v>
       </c>
       <c r="F15">
-        <v>1.925025464402805</v>
+        <v>3.2225652535347</v>
       </c>
       <c r="G15">
-        <v>-10.36627544956945</v>
+        <v>-9.426013174335406</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.783885819766148</v>
       </c>
       <c r="E16">
-        <v>-26.69116348444572</v>
+        <v>-24.12833721902245</v>
       </c>
       <c r="F16">
-        <v>2.632282239443411</v>
+        <v>3.377522973371986</v>
       </c>
       <c r="G16">
-        <v>-10.34899623649316</v>
+        <v>-8.515881502427405</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.165411724030979</v>
       </c>
       <c r="E17">
-        <v>-26.01703083504485</v>
+        <v>-26.09289339310417</v>
       </c>
       <c r="F17">
-        <v>2.926508400508962</v>
+        <v>3.671419444211223</v>
       </c>
       <c r="G17">
-        <v>-10.32846925714554</v>
+        <v>-8.395642354911386</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.596155597394374</v>
       </c>
       <c r="E18">
-        <v>-27.0756927081663</v>
+        <v>-25.69942230540124</v>
       </c>
       <c r="F18">
-        <v>3.487101070149111</v>
+        <v>3.855051930063818</v>
       </c>
       <c r="G18">
-        <v>-8.892896518085482</v>
+        <v>-7.874091297200094</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.086529448254591</v>
       </c>
       <c r="E19">
-        <v>-26.54838023230944</v>
+        <v>-26.28544457654587</v>
       </c>
       <c r="F19">
-        <v>3.031262085532182</v>
+        <v>3.951752227197021</v>
       </c>
       <c r="G19">
-        <v>-8.842788497148245</v>
+        <v>-7.589239481725201</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.629066616704971</v>
       </c>
       <c r="E20">
-        <v>-27.60084136092292</v>
+        <v>-27.31699013292751</v>
       </c>
       <c r="F20">
-        <v>3.703275141053281</v>
+        <v>4.374771295315033</v>
       </c>
       <c r="G20">
-        <v>-8.038752263933905</v>
+        <v>-7.387776153862762</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.230951568563724</v>
       </c>
       <c r="E21">
-        <v>-30.10320517587934</v>
+        <v>-28.28662792130126</v>
       </c>
       <c r="F21">
-        <v>4.375284883104769</v>
+        <v>4.243345836656474</v>
       </c>
       <c r="G21">
-        <v>-8.302458353593074</v>
+        <v>-7.417274956997751</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.895759737643819</v>
       </c>
       <c r="E22">
-        <v>-29.48243298557987</v>
+        <v>-28.46107940978935</v>
       </c>
       <c r="F22">
-        <v>3.935102042400751</v>
+        <v>4.339446395790051</v>
       </c>
       <c r="G22">
-        <v>-8.550077035081806</v>
+        <v>-7.161299282072867</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.624229295019219</v>
       </c>
       <c r="E23">
-        <v>-29.59946009768522</v>
+        <v>-28.46825823556432</v>
       </c>
       <c r="F23">
-        <v>3.766033912224177</v>
+        <v>4.327928775421526</v>
       </c>
       <c r="G23">
-        <v>-8.597603029618432</v>
+        <v>-6.645695500540131</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.426235986955841</v>
       </c>
       <c r="E24">
-        <v>-29.37537565725976</v>
+        <v>-29.17996291121525</v>
       </c>
       <c r="F24">
-        <v>3.484559638957322</v>
+        <v>4.512995993615769</v>
       </c>
       <c r="G24">
-        <v>-6.569560966774085</v>
+        <v>-6.519925490607839</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.296214779429384</v>
       </c>
       <c r="E25">
-        <v>-32.36247737878222</v>
+        <v>-30.39307025387309</v>
       </c>
       <c r="F25">
-        <v>3.959267176275218</v>
+        <v>4.492891516749825</v>
       </c>
       <c r="G25">
-        <v>-8.776035674070366</v>
+        <v>-6.428985424265591</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.236091059071206</v>
       </c>
       <c r="E26">
-        <v>-30.7383204814891</v>
+        <v>-29.55378930935174</v>
       </c>
       <c r="F26">
-        <v>4.020296316309069</v>
+        <v>4.434294463410594</v>
       </c>
       <c r="G26">
-        <v>-8.048086981219431</v>
+        <v>-6.36062568789188</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.238470582680528</v>
       </c>
       <c r="E27">
-        <v>-31.5963677113817</v>
+        <v>-29.50695146863599</v>
       </c>
       <c r="F27">
-        <v>3.56248084706906</v>
+        <v>4.357652254568778</v>
       </c>
       <c r="G27">
-        <v>-7.553759462731971</v>
+        <v>-6.349652728375431</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.292565694232343</v>
       </c>
       <c r="E28">
-        <v>-30.2958248873079</v>
+        <v>-29.80274110258462</v>
       </c>
       <c r="F28">
-        <v>3.805885011238056</v>
+        <v>4.49432790582628</v>
       </c>
       <c r="G28">
-        <v>-7.205945625325495</v>
+        <v>-5.766600360331283</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.391579324845582</v>
       </c>
       <c r="E29">
-        <v>-31.47023468344665</v>
+        <v>-30.00846419574301</v>
       </c>
       <c r="F29">
-        <v>3.600048965520823</v>
+        <v>4.338089529984265</v>
       </c>
       <c r="G29">
-        <v>-7.340072628693941</v>
+        <v>-5.819956147539865</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.519091662511511</v>
       </c>
       <c r="E30">
-        <v>-30.68591318438676</v>
+        <v>-29.52422467453595</v>
       </c>
       <c r="F30">
-        <v>4.149241642963645</v>
+        <v>4.143295621746351</v>
       </c>
       <c r="G30">
-        <v>-7.938337805470505</v>
+        <v>-6.348587544582257</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.668500861274924</v>
       </c>
       <c r="E31">
-        <v>-30.64594060199094</v>
+        <v>-29.26569349938236</v>
       </c>
       <c r="F31">
-        <v>3.349176240848188</v>
+        <v>4.134463568497702</v>
       </c>
       <c r="G31">
-        <v>-6.770648347415404</v>
+        <v>-5.845421350281584</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.828865850931987</v>
       </c>
       <c r="E32">
-        <v>-29.62157387138427</v>
+        <v>-28.8923571801822</v>
       </c>
       <c r="F32">
-        <v>3.208928669349814</v>
+        <v>3.717562822016767</v>
       </c>
       <c r="G32">
-        <v>-6.799144624627405</v>
+        <v>-5.846530916732807</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.993195324113472</v>
       </c>
       <c r="E33">
-        <v>-31.67941117182164</v>
+        <v>-29.52354770109</v>
       </c>
       <c r="F33">
-        <v>3.588874289257058</v>
+        <v>3.988874683986078</v>
       </c>
       <c r="G33">
-        <v>-7.460524551894134</v>
+        <v>-5.929142707829405</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.161616390305743</v>
       </c>
       <c r="E34">
-        <v>-30.65956936495337</v>
+        <v>-29.29274128813531</v>
       </c>
       <c r="F34">
-        <v>4.20822140204297</v>
+        <v>4.034583997272554</v>
       </c>
       <c r="G34">
-        <v>-7.09672251461168</v>
+        <v>-5.816324601813626</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.330074389890114</v>
       </c>
       <c r="E35">
-        <v>-29.70929384777597</v>
+        <v>-28.96027464497712</v>
       </c>
       <c r="F35">
-        <v>3.412920769228415</v>
+        <v>3.991634804172206</v>
       </c>
       <c r="G35">
-        <v>-6.772507197564276</v>
+        <v>-6.26968301080504</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.506080134655382</v>
       </c>
       <c r="E36">
-        <v>-29.84862370469566</v>
+        <v>-28.02255013242336</v>
       </c>
       <c r="F36">
-        <v>3.62049141628711</v>
+        <v>4.364274223586758</v>
       </c>
       <c r="G36">
-        <v>-7.238029065605686</v>
+        <v>-5.884018598316603</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.692035339866511</v>
       </c>
       <c r="E37">
-        <v>-29.67068767190603</v>
+        <v>-28.35462429711135</v>
       </c>
       <c r="F37">
-        <v>4.036848753751809</v>
+        <v>4.385228605407974</v>
       </c>
       <c r="G37">
-        <v>-7.375061827704041</v>
+        <v>-6.299320183403358</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.893338954609753</v>
       </c>
       <c r="E38">
-        <v>-27.3573012020463</v>
+        <v>-27.57589302049467</v>
       </c>
       <c r="F38">
-        <v>3.819844658710033</v>
+        <v>4.463908598060677</v>
       </c>
       <c r="G38">
-        <v>-7.345928528811807</v>
+        <v>-5.901604573882342</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.117301613625186</v>
       </c>
       <c r="E39">
-        <v>-27.28560846815711</v>
+        <v>-26.89149363269883</v>
       </c>
       <c r="F39">
-        <v>3.677541079317912</v>
+        <v>4.720730657420218</v>
       </c>
       <c r="G39">
-        <v>-8.13512528977026</v>
+        <v>-6.558509684919903</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.361649408374117</v>
       </c>
       <c r="E40">
-        <v>-27.68332413783401</v>
+        <v>-26.65458615230796</v>
       </c>
       <c r="F40">
-        <v>3.803330326167822</v>
+        <v>4.781678617448595</v>
       </c>
       <c r="G40">
-        <v>-7.821769364849593</v>
+        <v>-6.557598535057604</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.632257506483739</v>
       </c>
       <c r="E41">
-        <v>-28.72310343566712</v>
+        <v>-26.8460907264958</v>
       </c>
       <c r="F41">
-        <v>3.794200060654166</v>
+        <v>4.662766476776726</v>
       </c>
       <c r="G41">
-        <v>-7.940100058069507</v>
+        <v>-6.958097198312746</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.922572550351599</v>
       </c>
       <c r="E42">
-        <v>-26.44649780530007</v>
+        <v>-25.89664169837205</v>
       </c>
       <c r="F42">
-        <v>3.920680165918011</v>
+        <v>4.658854925900706</v>
       </c>
       <c r="G42">
-        <v>-8.412781893152045</v>
+        <v>-6.915965002101361</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.228715813630924</v>
       </c>
       <c r="E43">
-        <v>-26.9054899548635</v>
+        <v>-25.25853815721407</v>
       </c>
       <c r="F43">
-        <v>4.365546595917458</v>
+        <v>5.126393771714776</v>
       </c>
       <c r="G43">
-        <v>-7.852373818318918</v>
+        <v>-6.901122919100882</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.546163325967009</v>
       </c>
       <c r="E44">
-        <v>-26.12767653794961</v>
+        <v>-24.60521309655059</v>
       </c>
       <c r="F44">
-        <v>3.654404777757721</v>
+        <v>5.082771944283354</v>
       </c>
       <c r="G44">
-        <v>-8.669907601069315</v>
+        <v>-6.962410148377265</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.861921027786214</v>
       </c>
       <c r="E45">
-        <v>-25.67006325454603</v>
+        <v>-24.31325480004912</v>
       </c>
       <c r="F45">
-        <v>4.544894765562773</v>
+        <v>5.2518616120124</v>
       </c>
       <c r="G45">
-        <v>-8.49872891046379</v>
+        <v>-7.31619736940821</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.176122978034284</v>
       </c>
       <c r="E46">
-        <v>-23.83283208004957</v>
+        <v>-23.84249244959112</v>
       </c>
       <c r="F46">
-        <v>4.039570769037407</v>
+        <v>4.986457666359855</v>
       </c>
       <c r="G46">
-        <v>-8.93213731466221</v>
+        <v>-7.218464145639883</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.477104440239159</v>
       </c>
       <c r="E47">
-        <v>-24.96133435480933</v>
+        <v>-23.32898940138933</v>
       </c>
       <c r="F47">
-        <v>5.01956419798014</v>
+        <v>5.209651322635348</v>
       </c>
       <c r="G47">
-        <v>-8.271511892582314</v>
+        <v>-7.50905829384293</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.763566447529539</v>
       </c>
       <c r="E48">
-        <v>-24.66586244152706</v>
+        <v>-22.80784029113851</v>
       </c>
       <c r="F48">
-        <v>4.278461987595951</v>
+        <v>5.171331046581843</v>
       </c>
       <c r="G48">
-        <v>-8.939977380669324</v>
+        <v>-7.779540571088336</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.034240607582302</v>
       </c>
       <c r="E49">
-        <v>-22.63156969609014</v>
+        <v>-22.45468442576569</v>
       </c>
       <c r="F49">
-        <v>4.680235088566961</v>
+        <v>5.130630042612692</v>
       </c>
       <c r="G49">
-        <v>-9.095453747931598</v>
+        <v>-7.304067850037897</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.281978607230872</v>
       </c>
       <c r="E50">
-        <v>-22.08690510331815</v>
+        <v>-21.86507793324773</v>
       </c>
       <c r="F50">
-        <v>4.228181742980826</v>
+        <v>5.248082599920829</v>
       </c>
       <c r="G50">
-        <v>-8.765379920021736</v>
+        <v>-7.616165396065648</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.514553720904799</v>
       </c>
       <c r="E51">
-        <v>-21.51137799719136</v>
+        <v>-20.71708463774055</v>
       </c>
       <c r="F51">
-        <v>4.439105621286053</v>
+        <v>5.180812539874286</v>
       </c>
       <c r="G51">
-        <v>-8.663157520928991</v>
+        <v>-8.018045143209489</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.724523443308699</v>
       </c>
       <c r="E52">
-        <v>-21.76253514563772</v>
+        <v>-20.35341699450459</v>
       </c>
       <c r="F52">
-        <v>4.025869572195104</v>
+        <v>5.567910283937301</v>
       </c>
       <c r="G52">
-        <v>-9.478889889911519</v>
+        <v>-7.745380283485914</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.918284886067788</v>
       </c>
       <c r="E53">
-        <v>-21.7490662813113</v>
+        <v>-19.88507596624898</v>
       </c>
       <c r="F53">
-        <v>4.450555315527549</v>
+        <v>5.412874697564151</v>
       </c>
       <c r="G53">
-        <v>-8.291521944500902</v>
+        <v>-8.0606694647763</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.097402023746802</v>
       </c>
       <c r="E54">
-        <v>-20.77992687829653</v>
+        <v>-19.50768611279578</v>
       </c>
       <c r="F54">
-        <v>4.202704475140325</v>
+        <v>5.14846313606016</v>
       </c>
       <c r="G54">
-        <v>-8.691232162889529</v>
+        <v>-8.105485506427351</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.258124001888138</v>
       </c>
       <c r="E55">
-        <v>-20.25582483479377</v>
+        <v>-18.77856079224286</v>
       </c>
       <c r="F55">
-        <v>4.400342997039454</v>
+        <v>5.460007146048637</v>
       </c>
       <c r="G55">
-        <v>-9.372525544524974</v>
+        <v>-8.400609296495979</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.411348760770262</v>
       </c>
       <c r="E56">
-        <v>-21.33524445811671</v>
+        <v>-18.52850424479758</v>
       </c>
       <c r="F56">
-        <v>4.032087297920516</v>
+        <v>5.025293186937901</v>
       </c>
       <c r="G56">
-        <v>-9.700782294199421</v>
+        <v>-8.462190234538864</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.548952315807994</v>
       </c>
       <c r="E57">
-        <v>-19.93048302566332</v>
+        <v>-17.05696332745228</v>
       </c>
       <c r="F57">
-        <v>3.792256710727198</v>
+        <v>5.315185329752005</v>
       </c>
       <c r="G57">
-        <v>-9.816914740473617</v>
+        <v>-8.448140512521787</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.68253836451349</v>
       </c>
       <c r="E58">
-        <v>-17.99913177612361</v>
+        <v>-17.45602879080975</v>
       </c>
       <c r="F58">
-        <v>4.424347427637778</v>
+        <v>5.167561974899106</v>
       </c>
       <c r="G58">
-        <v>-9.337656439766064</v>
+        <v>-8.106756939043223</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.814097299889041</v>
       </c>
       <c r="E59">
-        <v>-19.32471223466913</v>
+        <v>-17.43209798715609</v>
       </c>
       <c r="F59">
-        <v>4.336270435167718</v>
+        <v>5.239523907915104</v>
       </c>
       <c r="G59">
-        <v>-10.10394000082061</v>
+        <v>-8.451132425823204</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.943070471675735</v>
       </c>
       <c r="E60">
-        <v>-18.62314762446777</v>
+        <v>-16.82190817931228</v>
       </c>
       <c r="F60">
-        <v>3.637269169663411</v>
+        <v>5.328739077196611</v>
       </c>
       <c r="G60">
-        <v>-9.704020922864697</v>
+        <v>-8.956965495723699</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.082395135162219</v>
       </c>
       <c r="E61">
-        <v>-19.02654488723704</v>
+        <v>-16.59784242833778</v>
       </c>
       <c r="F61">
-        <v>3.703526964743732</v>
+        <v>4.860911959526367</v>
       </c>
       <c r="G61">
-        <v>-8.939113224209665</v>
+        <v>-9.010270373412753</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.221887224017694</v>
       </c>
       <c r="E62">
-        <v>-18.69710385852899</v>
+        <v>-16.44923222071277</v>
       </c>
       <c r="F62">
-        <v>3.734657011740937</v>
+        <v>4.77935421851634</v>
       </c>
       <c r="G62">
-        <v>-10.09622786129846</v>
+        <v>-8.875493294641121</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.374708321735413</v>
       </c>
       <c r="E63">
-        <v>-18.05724766219193</v>
+        <v>-15.48128478934823</v>
       </c>
       <c r="F63">
-        <v>3.70170952666199</v>
+        <v>4.834838267155851</v>
       </c>
       <c r="G63">
-        <v>-10.35383786233738</v>
+        <v>-9.182153965057879</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.537731285340715</v>
       </c>
       <c r="E64">
-        <v>-17.77027737249158</v>
+        <v>-15.66372290321397</v>
       </c>
       <c r="F64">
-        <v>3.586051213148317</v>
+        <v>4.852883422658435</v>
       </c>
       <c r="G64">
-        <v>-11.23966089135753</v>
+        <v>-9.392483381551738</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.708359004433939</v>
       </c>
       <c r="E65">
-        <v>-17.77848827128077</v>
+        <v>-14.56802684470903</v>
       </c>
       <c r="F65">
-        <v>3.650307672583475</v>
+        <v>4.592262470389654</v>
       </c>
       <c r="G65">
-        <v>-11.14897798335751</v>
+        <v>-9.514775879688667</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.894002704314993</v>
       </c>
       <c r="E66">
-        <v>-17.3513221800995</v>
+        <v>-14.89486380991641</v>
       </c>
       <c r="F66">
-        <v>3.499581253439688</v>
+        <v>4.765432675944891</v>
       </c>
       <c r="G66">
-        <v>-9.751977690258856</v>
+        <v>-9.488506567612886</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.078143443637302</v>
       </c>
       <c r="E67">
-        <v>-17.93447042900735</v>
+        <v>-14.67547042168234</v>
       </c>
       <c r="F67">
-        <v>3.994096712093326</v>
+        <v>4.550133361018077</v>
       </c>
       <c r="G67">
-        <v>-11.52320472379228</v>
+        <v>-9.335681411482888</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.268162619459778</v>
       </c>
       <c r="E68">
-        <v>-17.6377483991163</v>
+        <v>-14.5826586082064</v>
       </c>
       <c r="F68">
-        <v>3.389875588082533</v>
+        <v>4.72099739172392</v>
       </c>
       <c r="G68">
-        <v>-10.73704817491017</v>
+        <v>-9.937570301751917</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.45106441823682</v>
       </c>
       <c r="E69">
-        <v>-16.21757024622516</v>
+        <v>-14.15808412089183</v>
       </c>
       <c r="F69">
-        <v>4.113857100985661</v>
+        <v>4.838577517612087</v>
       </c>
       <c r="G69">
-        <v>-10.43842337634486</v>
+        <v>-9.597405945997403</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.619252454199833</v>
       </c>
       <c r="E70">
-        <v>-15.75611939555743</v>
+        <v>-14.57347170475588</v>
       </c>
       <c r="F70">
-        <v>3.347355489296834</v>
+        <v>4.728046798321744</v>
       </c>
       <c r="G70">
-        <v>-11.86090192590819</v>
+        <v>-10.01147525963715</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.7727119971275</v>
       </c>
       <c r="E71">
-        <v>-15.06919485527609</v>
+        <v>-13.71810537277347</v>
       </c>
       <c r="F71">
-        <v>4.308342856549735</v>
+        <v>4.547316911848559</v>
       </c>
       <c r="G71">
-        <v>-10.19743859686215</v>
+        <v>-9.38490047388685</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.892412021864677</v>
       </c>
       <c r="E72">
-        <v>-15.79848215107068</v>
+        <v>-13.84587061275917</v>
       </c>
       <c r="F72">
-        <v>3.226292906847298</v>
+        <v>4.205285667967448</v>
       </c>
       <c r="G72">
-        <v>-11.53854154289277</v>
+        <v>-9.480417175497321</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.985181772562505</v>
       </c>
       <c r="E73">
-        <v>-16.93021562424116</v>
+        <v>-14.42777705148089</v>
       </c>
       <c r="F73">
-        <v>3.225403240256691</v>
+        <v>4.598730363070713</v>
       </c>
       <c r="G73">
-        <v>-9.956154887123757</v>
+        <v>-9.499974263229351</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.03724522643392</v>
       </c>
       <c r="E74">
-        <v>-15.8875934532562</v>
+        <v>-14.32409213075655</v>
       </c>
       <c r="F74">
-        <v>3.491983467621211</v>
+        <v>4.48804888091306</v>
       </c>
       <c r="G74">
-        <v>-10.90416063081504</v>
+        <v>-9.900228821865223</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.04543455498653</v>
       </c>
       <c r="E75">
-        <v>-16.84521600126722</v>
+        <v>-13.8312388492618</v>
       </c>
       <c r="F75">
-        <v>4.204654452006515</v>
+        <v>4.407753571824898</v>
       </c>
       <c r="G75">
-        <v>-9.988263129477565</v>
+        <v>-9.446993117869592</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.01083355798655</v>
       </c>
       <c r="E76">
-        <v>-16.01754328239877</v>
+        <v>-14.75859279313746</v>
       </c>
       <c r="F76">
-        <v>3.378313235874257</v>
+        <v>4.436214619050284</v>
       </c>
       <c r="G76">
-        <v>-10.88455002281889</v>
+        <v>-9.248445991715428</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.919933053927281</v>
       </c>
       <c r="E77">
-        <v>-17.05660199806702</v>
+        <v>-14.58852709580838</v>
       </c>
       <c r="F77">
-        <v>3.709111817773406</v>
+        <v>4.728291995072972</v>
       </c>
       <c r="G77">
-        <v>-10.0203335160348</v>
+        <v>-9.278268527179716</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.784374293065492</v>
       </c>
       <c r="E78">
-        <v>-17.17052458470707</v>
+        <v>-14.60566739894595</v>
       </c>
       <c r="F78">
-        <v>3.759385435449308</v>
+        <v>4.374246110381658</v>
       </c>
       <c r="G78">
-        <v>-9.903677615470084</v>
+        <v>-9.380667151532361</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.595513038589171</v>
       </c>
       <c r="E79">
-        <v>-18.43607867997484</v>
+        <v>-15.55808181995563</v>
       </c>
       <c r="F79">
-        <v>3.525172835981776</v>
+        <v>4.051926697217564</v>
       </c>
       <c r="G79">
-        <v>-9.679532138600054</v>
+        <v>-9.319348593320882</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.358839107756213</v>
       </c>
       <c r="E80">
-        <v>-18.35211735983211</v>
+        <v>-15.93799682589432</v>
       </c>
       <c r="F80">
-        <v>2.799478259289658</v>
+        <v>4.318246817217606</v>
       </c>
       <c r="G80">
-        <v>-9.556398980704786</v>
+        <v>-8.996690585422078</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.080158649700246</v>
       </c>
       <c r="E81">
-        <v>-20.10625108214139</v>
+        <v>-15.83046187827186</v>
       </c>
       <c r="F81">
-        <v>3.743778993580566</v>
+        <v>4.530288991516612</v>
       </c>
       <c r="G81">
-        <v>-9.644837953728748</v>
+        <v>-8.736973713498129</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.754077562499505</v>
       </c>
       <c r="E82">
-        <v>-18.90143770249923</v>
+        <v>-16.96613674898961</v>
       </c>
       <c r="F82">
-        <v>3.226920809338619</v>
+        <v>3.976717563982592</v>
       </c>
       <c r="G82">
-        <v>-9.084185774276353</v>
+        <v>-8.775432592069818</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.398420321055921</v>
       </c>
       <c r="E83">
-        <v>-19.11003689450007</v>
+        <v>-18.13936910971777</v>
       </c>
       <c r="F83">
-        <v>3.285908852091972</v>
+        <v>4.196698811470029</v>
       </c>
       <c r="G83">
-        <v>-9.129689747127163</v>
+        <v>-8.437692312668153</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.010696835722039</v>
       </c>
       <c r="E84">
-        <v>-20.67651606951963</v>
+        <v>-18.5103256388288</v>
       </c>
       <c r="F84">
-        <v>3.394332204709594</v>
+        <v>4.066393305540055</v>
       </c>
       <c r="G84">
-        <v>-8.877869072219035</v>
+        <v>-7.733733751864957</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.605865359359979</v>
       </c>
       <c r="E85">
-        <v>-21.6829928423446</v>
+        <v>-19.88933716106825</v>
       </c>
       <c r="F85">
-        <v>3.095357841691197</v>
+        <v>4.161282791530739</v>
       </c>
       <c r="G85">
-        <v>-9.191718427867423</v>
+        <v>-8.125156161549095</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.19607774197183</v>
       </c>
       <c r="E86">
-        <v>-23.14239807619875</v>
+        <v>-20.70055070345641</v>
       </c>
       <c r="F86">
-        <v>3.306208823664977</v>
+        <v>4.06727634519144</v>
       </c>
       <c r="G86">
-        <v>-8.318655413036343</v>
+        <v>-7.861427880560899</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.786864449149887</v>
       </c>
       <c r="E87">
-        <v>-23.11250741429396</v>
+        <v>-20.96324547296314</v>
       </c>
       <c r="F87">
-        <v>3.12733945037848</v>
+        <v>4.075377778390819</v>
       </c>
       <c r="G87">
-        <v>-9.165633173285315</v>
+        <v>-7.010019686740808</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.401894045538931</v>
       </c>
       <c r="E88">
-        <v>-25.75052341754193</v>
+        <v>-22.72961870904669</v>
       </c>
       <c r="F88">
-        <v>3.066409714432965</v>
+        <v>3.914608232855491</v>
       </c>
       <c r="G88">
-        <v>-8.497111554189596</v>
+        <v>-7.40341190321894</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.043001982145111</v>
       </c>
       <c r="E89">
-        <v>-26.30479023489692</v>
+        <v>-24.29535861245043</v>
       </c>
       <c r="F89">
-        <v>3.33579645055817</v>
+        <v>3.766893757588283</v>
       </c>
       <c r="G89">
-        <v>-8.719789792599421</v>
+        <v>-6.780480411545536</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.727591590018781</v>
       </c>
       <c r="E90">
-        <v>-26.60292435663841</v>
+        <v>-25.62808674768598</v>
       </c>
       <c r="F90">
-        <v>3.043256845524719</v>
+        <v>3.493113360758629</v>
       </c>
       <c r="G90">
-        <v>-8.682030593578149</v>
+        <v>-6.869723493903562</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.461029356244756</v>
       </c>
       <c r="E91">
-        <v>-29.22176498319965</v>
+        <v>-26.91530814643539</v>
       </c>
       <c r="F91">
-        <v>2.830863443446926</v>
+        <v>3.545618600217673</v>
       </c>
       <c r="G91">
-        <v>-8.975942998156501</v>
+        <v>-7.14256980037622</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.241423832558822</v>
       </c>
       <c r="E92">
-        <v>-29.57596538122067</v>
+        <v>-28.79512427325098</v>
       </c>
       <c r="F92">
-        <v>2.392300889382783</v>
+        <v>3.464246413505872</v>
       </c>
       <c r="G92">
-        <v>-8.137690346331029</v>
+        <v>-6.34946475476487</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.075705136718617</v>
       </c>
       <c r="E93">
-        <v>-31.07564222868602</v>
+        <v>-30.54605171641749</v>
       </c>
       <c r="F93">
-        <v>2.850654797434611</v>
+        <v>3.426984790993145</v>
       </c>
       <c r="G93">
-        <v>-8.218490280681394</v>
+        <v>-6.844576802001959</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.948921964580554</v>
       </c>
       <c r="E94">
-        <v>-33.20341545462217</v>
+        <v>-32.47447287536755</v>
       </c>
       <c r="F94">
-        <v>2.785076263624586</v>
+        <v>3.092170283925224</v>
       </c>
       <c r="G94">
-        <v>-8.536480277251288</v>
+        <v>-6.790273314506802</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.860594020079902</v>
       </c>
       <c r="E95">
-        <v>-34.10582936449224</v>
+        <v>-34.61142469833158</v>
       </c>
       <c r="F95">
-        <v>2.520517252722896</v>
+        <v>3.1198592927312</v>
       </c>
       <c r="G95">
-        <v>-7.727260410651292</v>
+        <v>-6.520831418980956</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.796254149557115</v>
       </c>
       <c r="E96">
-        <v>-37.39077863617478</v>
+        <v>-36.19519369209639</v>
       </c>
       <c r="F96">
-        <v>2.001853227542847</v>
+        <v>2.58986485821566</v>
       </c>
       <c r="G96">
-        <v>-8.115619111557757</v>
+        <v>-5.979819871087505</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.74190464957807</v>
       </c>
       <c r="E97">
-        <v>-41.75399501503762</v>
+        <v>-38.29918147677525</v>
       </c>
       <c r="F97">
-        <v>1.953809574915282</v>
+        <v>2.438725912105279</v>
       </c>
       <c r="G97">
-        <v>-7.54411798295699</v>
+        <v>-6.687177621348329</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.687227222620201</v>
       </c>
       <c r="E98">
-        <v>-40.47595428992174</v>
+        <v>-40.54903627299909</v>
       </c>
       <c r="F98">
-        <v>1.33898369141385</v>
+        <v>2.23789154876615</v>
       </c>
       <c r="G98">
-        <v>-6.987381920391265</v>
+        <v>-6.735659148405303</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.61494126918809</v>
       </c>
       <c r="E99">
-        <v>-42.67909999498089</v>
+        <v>-42.20721420085953</v>
       </c>
       <c r="F99">
-        <v>0.7848208095542306</v>
+        <v>1.932707743696367</v>
       </c>
       <c r="G99">
-        <v>-7.703973874270857</v>
+        <v>-6.314710522767971</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.515680941863946</v>
       </c>
       <c r="E100">
-        <v>-46.32484704087393</v>
+        <v>-44.78740296622625</v>
       </c>
       <c r="F100">
-        <v>0.9443196394936643</v>
+        <v>1.809908903170563</v>
       </c>
       <c r="G100">
-        <v>-7.129753655178445</v>
+        <v>-6.642366801186461</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.388308711153235</v>
       </c>
       <c r="E101">
-        <v>-48.23004448039837</v>
+        <v>-46.92626318979404</v>
       </c>
       <c r="F101">
-        <v>1.358647476821504</v>
+        <v>1.564235012317897</v>
       </c>
       <c r="G101">
-        <v>-8.134417777986069</v>
+        <v>-6.601417272274849</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.21419134152285</v>
       </c>
       <c r="E102">
-        <v>-49.97616561975923</v>
+        <v>-49.67255445058312</v>
       </c>
       <c r="F102">
-        <v>0.5824456828458946</v>
+        <v>1.32801776373559</v>
       </c>
       <c r="G102">
-        <v>-8.127838701616463</v>
+        <v>-6.73806625491831</v>
       </c>
     </row>
   </sheetData>
